--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486763_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486763_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.417899999999999</v>
+        <v>9.205399999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1174</v>
+        <v>5.8553</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3005</v>
+        <v>3.3502</v>
       </c>
       <c r="G2" t="n">
         <v>6.7775</v>
@@ -610,13 +610,13 @@
         <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6565</v>
+        <v>0.131</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.173</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2543</v>
+        <v>0.304</v>
       </c>
       <c r="V2" t="n">
         <v>3.0692</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0997</v>
+        <v>5.3769</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2121</v>
+        <v>3.3156</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8875</v>
+        <v>2.0614</v>
       </c>
       <c r="G3" t="n">
         <v>4.1288</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3806</v>
+        <v>-0.1034</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3587</v>
+        <v>-0.2553</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0219</v>
+        <v>0.1519</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2983</v>
+        <v>3.7266</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1754</v>
+        <v>1.0912</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1229</v>
+        <v>2.6354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.158</v>
+        <v>2.2565</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.8961</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0541</v>
+        <v>1.5463</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1993</v>
+        <v>1.2844</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5851</v>
+        <v>0.0207</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3858</v>
+        <v>1.2637</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3573</v>
+        <v>0.972</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.311</v>
+        <v>0.6895</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6683</v>
+        <v>0.2826</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7031</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1749</v>
+        <v>0.0414</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8268</v>
+        <v>-0.1932</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3481</v>
+        <v>0.2346</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2277</v>
+        <v>0.6565</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5032</v>
+        <v>3.675</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0912</v>
+        <v>0.7756</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4119</v>
+        <v>2.8994</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2565</v>
+        <v>0.158</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7102000000000001</v>
+        <v>-2.8961</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5463</v>
+        <v>3.0541</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2844</v>
+        <v>-0.1993</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0207</v>
+        <v>-1.5851</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2637</v>
+        <v>1.3858</v>
       </c>
       <c r="M5" t="n">
-        <v>0.972</v>
+        <v>0.3573</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6895</v>
+        <v>-1.311</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2826</v>
+        <v>1.6683</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7723</v>
+        <v>2.7031</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1821</v>
+        <v>0.5516</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1932</v>
+        <v>0.427</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0111</v>
+        <v>0.1246</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3735</v>
+        <v>2.1764</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.36</v>
+        <v>-0.6563</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7335</v>
+        <v>2.8328</v>
       </c>
       <c r="G6" t="n">
         <v>0.3755</v>
@@ -922,13 +922,13 @@
         <v>2.8962</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7004</v>
+        <v>0.5033</v>
       </c>
       <c r="T6" t="n">
-        <v>0.413</v>
+        <v>0.1166</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2874</v>
+        <v>0.3867</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5985</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0541</v>
+        <v>1.5684</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0134</v>
+        <v>-1.2756</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0675</v>
+        <v>2.844</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2659</v>
@@ -1000,13 +1000,13 @@
         <v>2.7031</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.4482</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.966</v>
+        <v>-0.2281</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8998</v>
+        <v>0.6763</v>
       </c>
       <c r="V7" t="n">
         <v>0.6138</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0645</v>
+        <v>-0.0596</v>
       </c>
       <c r="E8" t="n">
         <v>-1.4494</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5139</v>
+        <v>1.3897</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5603</v>
@@ -1078,13 +1078,13 @@
         <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1381</v>
+        <v>0.0139</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1932</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3313</v>
+        <v>0.2071</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2856</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5585</v>
+        <v>-0.6247</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2624</v>
+        <v>-2.3037</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7038</v>
+        <v>1.679</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3473</v>
@@ -1156,13 +1156,13 @@
         <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>0.866</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4409</v>
+        <v>0.3996</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4251</v>
+        <v>0.4003</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6565</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9876</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="E10" t="n">
         <v>-1.0758</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0881</v>
+        <v>0.1378</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0002</v>
@@ -1234,13 +1234,13 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2152</v>
+        <v>-0.1655</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0888</v>
+        <v>-2.0143</v>
       </c>
       <c r="E11" t="n">
         <v>-2.2485</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1597</v>
+        <v>0.2342</v>
       </c>
       <c r="G11" t="n">
         <v>-2.166</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.309</v>
+        <v>-0.2345</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0882</v>
+        <v>-0.0137</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7376</v>
+        <v>-2.5501</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2322</v>
+        <v>-2.9702</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4946</v>
+        <v>0.4201</v>
       </c>
       <c r="G12" t="n">
         <v>-0.873</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2427</v>
+        <v>-0.0552</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5243</v>
+        <v>-0.2623</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2815</v>
+        <v>0.2071</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6565</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.4387</v>
+        <v>19.542</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.045600000000001</v>
+        <v>-0.9418000000000015</v>
       </c>
       <c r="F13" t="n">
-        <v>20.4839</v>
+        <v>20.484</v>
       </c>
       <c r="G13" t="n">
         <v>8.483600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>17.377</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8271000000000003</v>
+        <v>1.9307</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7966</v>
+        <v>-0.6930000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6237</v>
+        <v>2.6238</v>
       </c>
       <c r="V13" t="n">
         <v>2.3701</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4246</v>
+        <v>4.1582</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6326000000000001</v>
+        <v>1.2531</v>
       </c>
       <c r="F14" t="n">
-        <v>2.792</v>
+        <v>2.905</v>
       </c>
       <c r="G14" t="n">
         <v>1.8532</v>
@@ -1546,13 +1546,13 @@
         <v>1.5446</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5405</v>
+        <v>0.1931</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9933</v>
+        <v>-0.3727</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4528</v>
+        <v>0.5659</v>
       </c>
       <c r="V14" t="n">
         <v>2.498</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4768</v>
+        <v>2.3196</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6089</v>
+        <v>2.402</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1321</v>
+        <v>-0.0824</v>
       </c>
       <c r="G15" t="n">
         <v>2.8014</v>
@@ -1624,13 +1624,13 @@
         <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0882</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1107</v>
+        <v>-0.3176</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1989</v>
+        <v>0.2486</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1851</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5313</v>
+        <v>0.5988</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.173</v>
+        <v>-1.0696</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7043</v>
+        <v>1.6683</v>
       </c>
       <c r="G16" t="n">
         <v>0.9502</v>
@@ -1702,13 +1702,13 @@
         <v>0.3862</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1603</v>
+        <v>0.2278</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2484</v>
+        <v>-0.145</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4086</v>
+        <v>0.3727</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1761</v>
+        <v>0.234</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2484</v>
+        <v>0.4552</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0723</v>
+        <v>-0.2213</v>
       </c>
       <c r="G17" t="n">
         <v>0.1649</v>
@@ -1780,13 +1780,13 @@
         <v>0.3862</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.375</v>
+        <v>-0.3171</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6622</v>
+        <v>-0.4553</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2872</v>
+        <v>0.1382</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.269</v>
+        <v>0.1172</v>
       </c>
       <c r="E18" t="n">
         <v>-1.448</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1789</v>
+        <v>1.5651</v>
       </c>
       <c r="G18" t="n">
         <v>0.8618</v>
@@ -1858,13 +1858,13 @@
         <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5516</v>
+        <v>-0.1654</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.386</v>
+        <v>0.0002</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8682</v>
+        <v>-1.0488</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-1.3593</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.026</v>
+        <v>0.3106</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5975</v>
@@ -1936,13 +1936,13 @@
         <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6287</v>
+        <v>0.4482</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4409</v>
+        <v>-0.0762</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1879</v>
+        <v>0.5244</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.652</v>
+        <v>-1.2424</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9589</v>
+        <v>-1.6486</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3069</v>
+        <v>0.4062</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8838</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5405</v>
+        <v>-0.131</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4691</v>
+        <v>-0.1588</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.0279</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7333</v>
+        <v>-2.4116</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8002</v>
+        <v>-1.7485</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9331</v>
+        <v>-0.6631</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1665</v>
+        <v>-1.3909</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0828</v>
+        <v>0.6753</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0837</v>
+        <v>-2.0662</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.283</v>
+        <v>-0.4448</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3237</v>
+        <v>1.7795</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0407</v>
+        <v>-2.2243</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8835</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7591</v>
+        <v>-1.1043</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1244</v>
+        <v>0.1582</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2812</v>
+        <v>-0.4068</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5518</v>
+        <v>-0.3383</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2706</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8995</v>
+        <v>-0.6138</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8995</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0032</v>
+        <v>-2.7002</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2656</v>
+        <v>-1.5933</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7376</v>
+        <v>-1.1069</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3909</v>
+        <v>-1.1665</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6753</v>
+        <v>-1.0828</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0662</v>
+        <v>-0.0837</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4448</v>
+        <v>-0.283</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7795</v>
+        <v>-0.3237</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2243</v>
+        <v>0.0407</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.8835</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1043</v>
+        <v>-0.7591</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1582</v>
+        <v>-0.1244</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9984</v>
+        <v>-0.2482</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8554</v>
+        <v>-0.345</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1431</v>
+        <v>0.0968</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6138</v>
+        <v>-0.8995</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6138</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4785</v>
+        <v>-4.1846</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7839</v>
+        <v>-2.4044</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6946</v>
+        <v>-1.7802</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3295</v>
@@ -2248,13 +2248,13 @@
         <v>0.9654</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0095</v>
+        <v>0.3034</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5512</v>
+        <v>-0.0693</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4582</v>
+        <v>0.3727</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2277</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4574</v>
+        <v>-5.0157</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5429</v>
+        <v>-4.4737</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9144</v>
+        <v>-0.5419</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4986</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5513</v>
+        <v>-0.007</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0475</v>
+        <v>0.1167</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4962</v>
+        <v>-0.1237</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.585800000000001</v>
+        <v>-8.573499999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.1591</v>
+        <v>-8.8489</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5734</v>
+        <v>0.2754</v>
       </c>
       <c r="G25" t="n">
         <v>-5.2484</v>
@@ -2404,13 +2404,13 @@
         <v>1.1585</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0222</v>
+        <v>0.0345</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.607</v>
+        <v>-0.2967</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6292</v>
+        <v>0.3312</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6565</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.4386</v>
+        <v>-17.749</v>
       </c>
       <c r="E26" t="n">
-        <v>-20.4839</v>
+        <v>-20.484</v>
       </c>
       <c r="F26" t="n">
-        <v>2.045399999999999</v>
+        <v>2.734799999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-8.483699999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>3.791799999999999</v>
+        <v>3.7918</v>
       </c>
       <c r="I26" t="n">
         <v>-12.2755</v>
@@ -2482,13 +2482,13 @@
         <v>10.6193</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8270000000000001</v>
+        <v>-0.1375</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.623799999999999</v>
+        <v>-2.6237</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7967</v>
+        <v>2.4863</v>
       </c>
       <c r="V26" t="n">
         <v>-2.3702</v>
